--- a/output/pdf_financials_xlsx/SLI.xlsx
+++ b/output/pdf_financials_xlsx/SLI.xlsx
@@ -4530,31 +4530,31 @@
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>7.437154</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>9.847553</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>13.544859</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>15.716067</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>19.56342</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>21.945</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>27.338</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>36.04</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>34.781</v>
       </c>
     </row>
     <row r="93">
@@ -5611,22 +5611,22 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>3.695</v>
+        <v>3.651255</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-3.187671</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-7.623522</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-3.866496</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-1.650288</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-5.9242</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>-4.493</v>
@@ -8298,7 +8298,11 @@
           <t>Reserves 9 37,299</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -12290,7 +12294,11 @@
           <t>Reserves (Note 12) 36,040</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -16194,7 +16202,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -17420,7 +17432,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -18364,7 +18380,11 @@
           <t>Reserves (Note 13)</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -19342,7 +19362,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -20536,7 +20560,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -33220,7 +33248,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -36578,7 +36610,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>
@@ -37730,7 +37766,11 @@
           <t>Accounts payable related to exploration and evaluation expenditures $</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SLI.xlsx
+++ b/output/pdf_financials_xlsx/SLI.xlsx
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.335551</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1668,7 +1668,7 @@
         <v>-25.434376</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-38.1</v>
+        <v>-38.435551</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-41.989</v>
@@ -1758,7 +1758,7 @@
         <v>-25.434376</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-38.1</v>
+        <v>-38.435551</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-41.989</v>
@@ -1965,40 +1965,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.008939000000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.003431</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.286203</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>4.067672</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>13.513182</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>6.849114</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>4.141494</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>27.988471</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>129.065</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>44.975</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>31.177</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>38.667</v>
       </c>
     </row>
     <row r="35">
@@ -2051,40 +2051,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.008939000000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.003431</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.286203</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>4.067672</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>13.513182</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>6.849114</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>4.141494</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>27.988471</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>129.065</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>44.975</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>31.177</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>38.667</v>
       </c>
     </row>
     <row r="37">
@@ -2570,28 +2570,28 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.003431</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.286203</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.458106</v>
+        <v>0.390434</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>14.542286</v>
+        <v>1.029104</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>7.103638</v>
+        <v>0.254524</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>4.42311</v>
+        <v>0.281616</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>28.238142</v>
+        <v>0.249671</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>130.669</v>
+        <v>1.604</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>1.842</v>
@@ -2600,7 +2600,7 @@
         <v>1.657</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>41.517</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="49">
@@ -5891,13 +5891,13 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.109</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.314</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.638</v>
       </c>
       <c r="M124" s="3" t="n">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.109</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.314</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.638</v>
       </c>
       <c r="M125" s="3" t="n">
         <v>0</v>
@@ -6524,7 +6524,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6812,7 +6812,11 @@
           <t>Reclamation deposit —</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -10688,7 +10692,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -14534,7 +14538,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
@@ -14876,7 +14880,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -17642,7 +17650,11 @@
           <t>Reclamation deposit (Note 6)</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -18528,7 +18540,11 @@
           <t>Reclamation deposit (Note 5)</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -31044,7 +31060,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -33820,7 +33840,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -36458,7 +36482,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>
@@ -42160,7 +42188,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">

--- a/output/pdf_financials_xlsx/SLI.xlsx
+++ b/output/pdf_financials_xlsx/SLI.xlsx
@@ -1707,19 +1707,19 @@
         <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.02774</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.191034</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.191</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="M28" s="1" t="inlineStr">
         <is>
@@ -1752,19 +1752,19 @@
         <v>-8.578841000000001</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-9.527367999999999</v>
+        <v>-9.499628</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-25.434376</v>
+        <v>-25.243342</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-38.435551</v>
+        <v>-38.244551</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-41.989</v>
+        <v>-41.879</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>182.489</v>
+        <v>182.574</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -4849,13 +4849,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.02774</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.191034</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.191035</v>
       </c>
       <c r="K100" s="3" t="n">
         <v>0</v>
@@ -32572,7 +32572,11 @@
           <t>Amortisation of intangible asset</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -39368,7 +39372,11 @@
           <t>Amortisation of intangible assets (Note 9)</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
@@ -41170,7 +41178,11 @@
           <t>Amortisation of intangible assets (Note 7)</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E463" t="inlineStr">
         <is>
           <t>-</t>
@@ -41662,7 +41674,11 @@
           <t>Amortisation of intangible asset (Note 7)</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E470" t="inlineStr">
         <is>
           <t>-</t>
@@ -42554,7 +42570,11 @@
           <t>Amortisation of intangible asset (Note 6)</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E482" t="inlineStr">
         <is>
           <t>-</t>
@@ -43814,7 +43834,11 @@
           <t>Amortisation of intangible asset (Note 7)</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SLI.xlsx
+++ b/output/pdf_financials_xlsx/SLI.xlsx
@@ -714,13 +714,13 @@
         <v>3.558369</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>6.03</v>
+        <v>8.717000000000001</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>9.169</v>
+        <v>12.413</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>12.508</v>
+        <v>15.88</v>
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
@@ -849,13 +849,13 @@
         <v>3.712599</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>6.675</v>
+        <v>9.362</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>10.064</v>
+        <v>13.308</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>15.987</v>
+        <v>19.359</v>
       </c>
       <c r="M10" s="1" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>-0.136017</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-0.374873</v>
+        <v>-0.357952</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-19.911856</v>
@@ -1156,7 +1156,7 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.016921</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -1650,7 +1650,7 @@
         <v>-0.136017</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.374873</v>
+        <v>-0.357952</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-19.911856</v>
@@ -1740,7 +1740,7 @@
         <v>-0.136017</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.374873</v>
+        <v>-0.357952</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-19.911856</v>
@@ -1852,7 +1852,7 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-4.727170123368497</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000144</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0.000549</v>
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.08704000000000001</v>
+        <v>0.086896</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.097084</v>
@@ -5261,28 +5261,28 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.063721</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.033425</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.008257</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.001335</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.046405</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.150167</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.173662</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0</v>
@@ -29092,7 +29092,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -29244,7 +29248,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -32210,7 +32218,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -32796,7 +32808,11 @@
           <t>Interest and accretion expense</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -36566,7 +36582,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E402" t="inlineStr">
         <is>
           <t>-</t>
@@ -37878,7 +37898,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E419" s="5" t="n">
         <v>0.063721</v>
       </c>
@@ -37952,7 +37976,11 @@
           <t>GST Receivables</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E420" s="5" t="n">
         <v>-0.000144</v>
       </c>
@@ -38778,7 +38806,11 @@
           <t>Management and directors’ fees (Note 13)</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
           <t>-</t>
@@ -40956,7 +40988,11 @@
           <t>Management and director fees (Note 11)</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
@@ -46448,7 +46484,11 @@
           <t>Deferred income tax recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr">
         <is>
           <t>-</t>
